--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260603.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260603.xlsx
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,192,441</t>
+          <t>558,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>558,000</t>
+          <t>1,192,441</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,115,107</t>
+          <t>178,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>178,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>2,115,107</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>202606WVHFM6F</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,178,076</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>202606WVHFM6F</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>1,178,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,709,000</t>
+          <t>325,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>325,000</t>
+          <t>1,709,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>174,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>174,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
